--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T16:30:02+00:00</t>
+    <t>2026-02-16T17:09:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T08:04:39+00:00</t>
+    <t>2026-02-17T08:46:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T08:46:02+00:00</t>
+    <t>2026-02-17T09:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:04:14+00:00</t>
+    <t>2026-02-17T09:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:55:45+00:00</t>
+    <t>2026-02-17T10:22:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:22:56+00:00</t>
+    <t>2026-04-14T15:08:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T15:08:12+00:00</t>
+    <t>2026-04-14T15:34:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6268" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6269" uniqueCount="949">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T15:34:16+00:00</t>
+    <t>2026-04-30T09:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,7 +469,11 @@
     <t>Full representation of the dosage instructions</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `MedicationRequest.renderedDosageInstruction` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -4397,7 +4401,9 @@
       <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -4455,7 +4461,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -4467,7 +4473,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -4478,13 +4484,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>81</v>
@@ -4506,13 +4512,13 @@
         <v>81</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -4572,7 +4578,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>141</v>
@@ -4595,10 +4601,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -4621,13 +4627,13 @@
         <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -4678,7 +4684,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -4699,7 +4705,7 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>81</v>
@@ -4710,10 +4716,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4784,7 +4790,7 @@
         <v>138</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>81</v>
@@ -4793,7 +4799,7 @@
         <v>139</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -4825,10 +4831,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4854,13 +4860,13 @@
         <v>104</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4868,7 +4874,7 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>81</v>
@@ -4910,7 +4916,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -4942,17 +4948,17 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>79</v>
@@ -4970,13 +4976,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -5003,13 +5009,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -5027,7 +5033,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -5059,10 +5065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -5085,13 +5091,13 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -5142,7 +5148,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -5163,7 +5169,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -5174,14 +5180,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -5203,13 +5209,13 @@
         <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -5250,7 +5256,7 @@
         <v>138</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
@@ -5259,7 +5265,7 @@
         <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -5280,7 +5286,7 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -5291,10 +5297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -5317,19 +5323,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -5378,7 +5384,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -5399,21 +5405,21 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5436,19 +5442,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -5497,7 +5503,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -5518,25 +5524,25 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -5558,16 +5564,16 @@
         <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5616,7 +5622,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -5648,10 +5654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5674,16 +5680,16 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5733,7 +5739,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -5748,27 +5754,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5794,13 +5800,13 @@
         <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5826,13 +5832,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -5850,7 +5856,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -5865,16 +5871,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -5882,10 +5888,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5908,16 +5914,16 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5943,13 +5949,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -5967,7 +5973,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5982,13 +5988,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -5999,10 +6005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -6028,13 +6034,13 @@
         <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -6045,7 +6051,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -6060,13 +6066,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -6084,7 +6090,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -6099,16 +6105,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -6116,10 +6122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6142,16 +6148,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -6177,13 +6183,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -6201,7 +6207,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -6219,13 +6225,13 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -6233,10 +6239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6262,10 +6268,10 @@
         <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6292,13 +6298,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -6316,7 +6322,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -6331,16 +6337,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -6348,10 +6354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6374,16 +6380,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -6433,7 +6439,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -6454,7 +6460,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -6465,10 +6471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6491,13 +6497,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6548,7 +6554,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -6569,7 +6575,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -6580,10 +6586,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6606,16 +6612,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6641,29 +6647,29 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>90</v>
@@ -6678,30 +6684,30 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>81</v>
@@ -6723,16 +6729,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6782,7 +6788,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>90</v>
@@ -6797,30 +6803,30 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>81</v>
@@ -6842,16 +6848,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6877,11 +6883,11 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -6899,7 +6905,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -6914,27 +6920,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6957,16 +6963,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -7016,7 +7022,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -7031,27 +7037,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7074,16 +7080,16 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -7133,7 +7139,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -7148,27 +7154,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7191,13 +7197,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7236,7 +7242,7 @@
         <v>81</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -7246,7 +7252,7 @@
         <v>139</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -7261,16 +7267,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -7278,10 +7284,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7304,13 +7310,13 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7361,7 +7367,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -7382,7 +7388,7 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -7393,14 +7399,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -7422,13 +7428,13 @@
         <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7469,7 +7475,7 @@
         <v>138</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>81</v>
@@ -7478,7 +7484,7 @@
         <v>139</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -7499,7 +7505,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -7510,13 +7516,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="B37" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="C37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>81</v>
@@ -7538,13 +7544,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7595,7 +7601,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7627,10 +7633,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7653,16 +7659,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7712,7 +7718,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7721,7 +7727,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -7744,10 +7750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7773,13 +7779,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7805,13 +7811,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -7829,7 +7835,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7861,10 +7867,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7887,16 +7893,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7946,7 +7952,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7967,7 +7973,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -7978,10 +7984,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8004,16 +8010,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8063,7 +8069,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -8095,13 +8101,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
@@ -8123,13 +8129,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8180,7 +8186,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -8195,16 +8201,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -8212,10 +8218,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8238,13 +8244,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8295,7 +8301,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -8316,7 +8322,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -8327,14 +8333,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -8356,13 +8362,13 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8403,7 +8409,7 @@
         <v>138</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>81</v>
@@ -8412,7 +8418,7 @@
         <v>139</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -8433,7 +8439,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -8444,13 +8450,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>81</v>
@@ -8472,13 +8478,13 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8529,7 +8535,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8561,10 +8567,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8587,16 +8593,16 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8646,7 +8652,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8655,7 +8661,7 @@
         <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>102</v>
@@ -8678,10 +8684,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8707,13 +8713,13 @@
         <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8739,13 +8745,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -8763,7 +8769,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8795,10 +8801,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8821,16 +8827,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8880,7 +8886,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8901,7 +8907,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -8912,10 +8918,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8938,16 +8944,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8997,7 +9003,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -9029,13 +9035,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>81</v>
@@ -9057,13 +9063,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9114,7 +9120,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -9129,16 +9135,16 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -9146,10 +9152,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9172,13 +9178,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9229,7 +9235,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -9250,7 +9256,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -9261,14 +9267,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -9290,13 +9296,13 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9337,7 +9343,7 @@
         <v>138</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>81</v>
@@ -9346,7 +9352,7 @@
         <v>139</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -9367,7 +9373,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -9378,13 +9384,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>81</v>
@@ -9406,13 +9412,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9463,7 +9469,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -9495,10 +9501,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9521,16 +9527,16 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9580,7 +9586,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -9589,7 +9595,7 @@
         <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>102</v>
@@ -9612,10 +9618,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9641,13 +9647,13 @@
         <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9673,13 +9679,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -9697,7 +9703,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9729,10 +9735,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9755,16 +9761,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9814,7 +9820,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9835,7 +9841,7 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -9846,10 +9852,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9872,16 +9878,16 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9931,7 +9937,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9963,10 +9969,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9989,13 +9995,13 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -10046,7 +10052,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -10061,27 +10067,27 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10104,13 +10110,13 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10161,7 +10167,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -10176,16 +10182,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -10193,10 +10199,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10219,13 +10225,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10276,7 +10282,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -10291,16 +10297,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -10308,10 +10314,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10334,16 +10340,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10369,13 +10375,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -10393,7 +10399,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -10408,13 +10414,13 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -10425,10 +10431,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10451,13 +10457,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10508,7 +10514,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10529,10 +10535,10 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -10540,10 +10546,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10566,16 +10572,16 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10601,13 +10607,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -10625,7 +10631,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10640,27 +10646,27 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10683,16 +10689,16 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10742,7 +10748,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10757,16 +10763,16 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -10774,10 +10780,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10800,13 +10806,13 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10857,7 +10863,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10872,13 +10878,13 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -10889,10 +10895,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10918,10 +10924,10 @@
         <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10972,7 +10978,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10993,7 +10999,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -11004,10 +11010,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11030,13 +11036,13 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11087,7 +11093,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -11102,13 +11108,13 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -11119,10 +11125,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11145,17 +11151,17 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -11204,7 +11210,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -11219,13 +11225,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -11236,10 +11242,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11262,16 +11268,16 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11297,13 +11303,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -11321,7 +11327,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -11342,7 +11348,7 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -11353,10 +11359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11379,13 +11385,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11436,7 +11442,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -11451,13 +11457,13 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -11468,10 +11474,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11494,13 +11500,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11551,7 +11557,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11566,13 +11572,13 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -11583,10 +11589,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11609,13 +11615,13 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11666,7 +11672,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11687,7 +11693,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -11698,14 +11704,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11727,13 +11733,13 @@
         <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11774,7 +11780,7 @@
         <v>138</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>81</v>
@@ -11783,7 +11789,7 @@
         <v>139</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11804,7 +11810,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -11815,13 +11821,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="B74" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="C74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>81</v>
@@ -11843,16 +11849,16 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11902,7 +11908,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11934,10 +11940,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11960,16 +11966,16 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12019,7 +12025,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -12040,7 +12046,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -12051,10 +12057,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12077,13 +12083,13 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12134,7 +12140,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -12155,7 +12161,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -12166,10 +12172,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12192,13 +12198,13 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12249,7 +12255,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>90</v>
@@ -12270,7 +12276,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -12281,10 +12287,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12307,16 +12313,16 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12366,7 +12372,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -12381,13 +12387,13 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -12398,10 +12404,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12424,13 +12430,13 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12481,7 +12487,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12502,7 +12508,7 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -12513,14 +12519,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12542,13 +12548,13 @@
         <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12589,7 +12595,7 @@
         <v>138</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>81</v>
@@ -12598,7 +12604,7 @@
         <v>139</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12619,7 +12625,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -12630,14 +12636,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12659,16 +12665,16 @@
         <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -12717,7 +12723,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12749,10 +12755,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12775,17 +12781,17 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12834,7 +12840,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12855,21 +12861,21 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12892,17 +12898,17 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12951,7 +12957,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12972,21 +12978,21 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13009,19 +13015,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13046,13 +13052,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -13070,7 +13076,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -13091,21 +13097,21 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13128,13 +13134,13 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13185,7 +13191,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -13206,21 +13212,21 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13243,19 +13249,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -13304,7 +13310,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -13325,7 +13331,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -13336,10 +13342,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13362,13 +13368,13 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13419,7 +13425,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13440,7 +13446,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13451,14 +13457,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13480,13 +13486,13 @@
         <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13527,7 +13533,7 @@
         <v>138</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>81</v>
@@ -13536,7 +13542,7 @@
         <v>139</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13557,7 +13563,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -13568,14 +13574,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13597,16 +13603,16 @@
         <v>135</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13655,7 +13661,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13687,10 +13693,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13713,17 +13719,17 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13772,7 +13778,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13793,7 +13799,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -13804,10 +13810,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13830,17 +13836,17 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13889,7 +13895,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13901,7 +13907,7 @@
         <v>81</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>81</v>
@@ -13910,7 +13916,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13921,10 +13927,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13947,13 +13953,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14004,7 +14010,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -14025,7 +14031,7 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -14036,14 +14042,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -14065,13 +14071,13 @@
         <v>135</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14112,7 +14118,7 @@
         <v>138</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>81</v>
@@ -14121,7 +14127,7 @@
         <v>139</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -14142,7 +14148,7 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
@@ -14153,13 +14159,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="B94" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="C94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>81</v>
@@ -14181,13 +14187,13 @@
         <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14238,7 +14244,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -14270,10 +14276,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14296,13 +14302,13 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14353,7 +14359,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14374,7 +14380,7 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
@@ -14385,10 +14391,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14411,19 +14417,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -14472,7 +14478,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14493,7 +14499,7 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -14504,10 +14510,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14530,13 +14536,13 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14587,7 +14593,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14608,7 +14614,7 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
@@ -14619,10 +14625,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14645,19 +14651,19 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14706,7 +14712,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14727,7 +14733,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -14738,10 +14744,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14764,19 +14770,19 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14825,7 +14831,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14846,7 +14852,7 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
@@ -14857,10 +14863,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14886,10 +14892,10 @@
         <v>110</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14916,13 +14922,13 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -14940,7 +14946,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14961,7 +14967,7 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
@@ -14972,10 +14978,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14998,13 +15004,13 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -15012,7 +15018,7 @@
         <v>81</v>
       </c>
       <c r="Q101" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="R101" t="s" s="2">
         <v>81</v>
@@ -15057,7 +15063,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -15078,7 +15084,7 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
@@ -15089,10 +15095,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15115,13 +15121,13 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15172,7 +15178,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -15193,7 +15199,7 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
@@ -15204,10 +15210,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15230,13 +15236,13 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15287,7 +15293,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -15308,7 +15314,7 @@
         <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
@@ -15319,10 +15325,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15345,13 +15351,13 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15402,7 +15408,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15423,7 +15429,7 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
@@ -15434,10 +15440,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15463,10 +15469,10 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15493,13 +15499,13 @@
         <v>81</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>81</v>
@@ -15517,7 +15523,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15538,7 +15544,7 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
@@ -15549,10 +15555,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15578,13 +15584,13 @@
         <v>110</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15610,11 +15616,11 @@
         <v>81</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -15632,7 +15638,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15653,7 +15659,7 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
@@ -15664,10 +15670,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15690,16 +15696,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15749,7 +15755,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15770,7 +15776,7 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
@@ -15781,10 +15787,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15810,16 +15816,16 @@
         <v>110</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -15844,13 +15850,13 @@
         <v>81</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>81</v>
@@ -15868,7 +15874,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15889,7 +15895,7 @@
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
@@ -15900,10 +15906,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15926,13 +15932,13 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15983,7 +15989,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -16004,7 +16010,7 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -16015,10 +16021,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16041,16 +16047,16 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16079,10 +16085,10 @@
         <v>114</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>81</v>
@@ -16100,7 +16106,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -16121,7 +16127,7 @@
         <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
@@ -16132,10 +16138,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16158,16 +16164,16 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -16193,13 +16199,13 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -16217,7 +16223,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -16238,21 +16244,21 @@
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16275,19 +16281,19 @@
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -16312,13 +16318,13 @@
         <v>81</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -16336,7 +16342,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -16357,21 +16363,21 @@
         <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16394,17 +16400,17 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -16429,11 +16435,11 @@
         <v>81</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -16451,7 +16457,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -16472,21 +16478,21 @@
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16509,19 +16515,19 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -16546,11 +16552,11 @@
         <v>81</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>81</v>
@@ -16568,7 +16574,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16589,21 +16595,21 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16626,13 +16632,13 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16683,7 +16689,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16710,15 +16716,15 @@
         <v>81</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16741,13 +16747,13 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16798,7 +16804,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16819,7 +16825,7 @@
         <v>81</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
@@ -16830,14 +16836,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16859,13 +16865,13 @@
         <v>135</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16906,7 +16912,7 @@
         <v>138</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>81</v>
@@ -16915,7 +16921,7 @@
         <v>139</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16936,7 +16942,7 @@
         <v>81</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
@@ -16947,13 +16953,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="B118" t="s" s="2">
-        <v>705</v>
-      </c>
       <c r="C118" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>81</v>
@@ -16975,13 +16981,13 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -17032,7 +17038,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -17064,10 +17070,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17090,17 +17096,17 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -17125,13 +17131,13 @@
         <v>81</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>81</v>
@@ -17149,7 +17155,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -17176,15 +17182,15 @@
         <v>81</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17207,19 +17213,19 @@
         <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -17256,17 +17262,17 @@
         <v>81</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17287,24 +17293,24 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
@@ -17326,19 +17332,19 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -17387,7 +17393,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17408,24 +17414,24 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>81</v>
@@ -17447,19 +17453,19 @@
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -17508,7 +17514,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17529,21 +17535,21 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17566,19 +17572,19 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -17615,17 +17621,17 @@
         <v>81</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC123" s="2"/>
       <c r="AD123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17646,24 +17652,24 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>81</v>
@@ -17685,19 +17691,19 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17746,7 +17752,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17767,24 +17773,24 @@
         <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>81</v>
@@ -17806,19 +17812,19 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17867,7 +17873,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17888,24 +17894,24 @@
         <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>81</v>
@@ -17927,19 +17933,19 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
@@ -17988,7 +17994,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -18009,21 +18015,21 @@
         <v>81</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18046,19 +18052,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -18107,7 +18113,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -18128,21 +18134,21 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18165,13 +18171,13 @@
         <v>81</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18222,7 +18228,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -18243,7 +18249,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -18254,14 +18260,14 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -18283,13 +18289,13 @@
         <v>135</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18330,7 +18336,7 @@
         <v>138</v>
       </c>
       <c r="AC129" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD129" t="s" s="2">
         <v>81</v>
@@ -18339,7 +18345,7 @@
         <v>139</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -18360,7 +18366,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -18371,10 +18377,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18397,13 +18403,13 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18454,7 +18460,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -18475,7 +18481,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -18486,10 +18492,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18512,13 +18518,13 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18569,7 +18575,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18590,7 +18596,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -18601,10 +18607,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18627,19 +18633,19 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
@@ -18688,7 +18694,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18709,7 +18715,7 @@
         <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>81</v>
@@ -18720,10 +18726,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18746,17 +18752,17 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -18805,7 +18811,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18826,7 +18832,7 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
@@ -18837,10 +18843,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18863,13 +18869,13 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18920,7 +18926,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18938,10 +18944,10 @@
         <v>81</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
@@ -18952,10 +18958,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18978,13 +18984,13 @@
         <v>81</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19035,7 +19041,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -19056,7 +19062,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -19067,14 +19073,14 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -19096,13 +19102,13 @@
         <v>135</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19152,7 +19158,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -19173,7 +19179,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -19184,14 +19190,14 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -19213,16 +19219,16 @@
         <v>135</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -19271,7 +19277,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -19303,10 +19309,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19329,16 +19335,16 @@
         <v>81</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19388,7 +19394,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19409,7 +19415,7 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>81</v>
@@ -19420,10 +19426,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19446,13 +19452,13 @@
         <v>81</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19503,7 +19509,7 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19524,7 +19530,7 @@
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
@@ -19535,14 +19541,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -19564,13 +19570,13 @@
         <v>135</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19620,7 +19626,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19641,7 +19647,7 @@
         <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>81</v>
@@ -19652,14 +19658,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19681,16 +19687,16 @@
         <v>135</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -19739,7 +19745,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19771,10 +19777,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19797,13 +19803,13 @@
         <v>81</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19854,7 +19860,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19875,7 +19881,7 @@
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
@@ -19886,10 +19892,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19912,13 +19918,13 @@
         <v>81</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19969,7 +19975,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19990,7 +19996,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -20001,10 +20007,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20027,13 +20033,13 @@
         <v>81</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -20084,7 +20090,7 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -20105,7 +20111,7 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -20116,10 +20122,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20142,19 +20148,19 @@
         <v>81</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>81</v>
@@ -20203,7 +20209,7 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -20221,10 +20227,10 @@
         <v>81</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>81</v>
@@ -20235,10 +20241,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20261,13 +20267,13 @@
         <v>81</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20318,7 +20324,7 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20339,7 +20345,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -20350,14 +20356,14 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20379,13 +20385,13 @@
         <v>135</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20426,7 +20432,7 @@
         <v>138</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>81</v>
@@ -20435,7 +20441,7 @@
         <v>139</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20456,7 +20462,7 @@
         <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>81</v>
@@ -20467,10 +20473,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20493,16 +20499,16 @@
         <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20552,7 +20558,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20561,7 +20567,7 @@
         <v>90</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>102</v>
@@ -20573,21 +20579,21 @@
         <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20610,23 +20616,23 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q149" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="R149" t="s" s="2">
         <v>81</v>
@@ -20671,7 +20677,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20680,7 +20686,7 @@
         <v>90</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>102</v>
@@ -20692,21 +20698,21 @@
         <v>81</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20729,16 +20735,16 @@
         <v>81</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20788,7 +20794,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20806,24 +20812,24 @@
         <v>81</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20846,13 +20852,13 @@
         <v>81</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20903,7 +20909,7 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20921,24 +20927,24 @@
         <v>81</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20961,16 +20967,16 @@
         <v>81</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21020,7 +21026,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -21038,10 +21044,10 @@
         <v>81</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>81</v>
@@ -21052,10 +21058,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21078,13 +21084,13 @@
         <v>81</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21135,7 +21141,7 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21156,7 +21162,7 @@
         <v>81</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>
@@ -21167,14 +21173,14 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -21196,13 +21202,13 @@
         <v>135</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21243,7 +21249,7 @@
         <v>138</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>81</v>
@@ -21252,7 +21258,7 @@
         <v>139</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21273,7 +21279,7 @@
         <v>81</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>81</v>
@@ -21284,10 +21290,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21310,19 +21316,19 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
@@ -21371,7 +21377,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21392,21 +21398,21 @@
         <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21432,20 +21438,20 @@
         <v>110</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q156" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="R156" t="s" s="2">
         <v>81</v>
@@ -21466,13 +21472,13 @@
         <v>81</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>81</v>
@@ -21490,7 +21496,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21511,21 +21517,21 @@
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21548,17 +21554,17 @@
         <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21607,7 +21613,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21628,21 +21634,21 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21668,14 +21674,14 @@
         <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>81</v>
@@ -21724,7 +21730,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21733,7 +21739,7 @@
         <v>90</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>102</v>
@@ -21745,21 +21751,21 @@
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21785,16 +21791,16 @@
         <v>110</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
@@ -21843,7 +21849,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21864,21 +21870,21 @@
         <v>81</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21901,13 +21907,13 @@
         <v>81</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21958,7 +21964,7 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21979,10 +21985,10 @@
         <v>81</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>81</v>
@@ -21990,10 +21996,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22016,13 +22022,13 @@
         <v>81</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -22073,7 +22079,7 @@
         <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22091,10 +22097,10 @@
         <v>81</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>81</v>
@@ -22105,10 +22111,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22131,13 +22137,13 @@
         <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22188,7 +22194,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22209,7 +22215,7 @@
         <v>81</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>81</v>
@@ -22220,14 +22226,14 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -22249,13 +22255,13 @@
         <v>135</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22305,7 +22311,7 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22326,7 +22332,7 @@
         <v>81</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>81</v>
@@ -22337,14 +22343,14 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -22366,16 +22372,16 @@
         <v>135</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22424,7 +22430,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22456,10 +22462,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22482,16 +22488,16 @@
         <v>81</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22517,13 +22523,13 @@
         <v>81</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>81</v>
@@ -22541,7 +22547,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>90</v>
@@ -22559,24 +22565,24 @@
         <v>81</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22599,13 +22605,13 @@
         <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22632,13 +22638,13 @@
         <v>81</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>81</v>
@@ -22656,7 +22662,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22674,24 +22680,24 @@
         <v>81</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22714,13 +22720,13 @@
         <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -22771,7 +22777,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22786,13 +22792,13 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>81</v>
@@ -22803,14 +22809,14 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -22829,16 +22835,16 @@
         <v>81</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22888,7 +22894,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22909,7 +22915,7 @@
         <v>81</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>81</v>
@@ -22920,10 +22926,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22946,16 +22952,16 @@
         <v>81</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -23005,7 +23011,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -23020,13 +23026,13 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>81</v>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:49:26+00:00</t>
+    <t>2026-05-12T12:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T12:57:02+00:00</t>
+    <t>2026-05-12T16:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T16:45:43+00:00</t>
+    <t>2026-05-18T17:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
